--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18">

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18">

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18">

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -807,55 +807,55 @@
         <v>3.34</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q6">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G28">

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>2.55</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>3.05</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL20">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
+        <v>4.4</v>
+      </c>
+      <c r="Q17">
+        <v>2.38</v>
+      </c>
+      <c r="R17">
+        <v>2.01</v>
+      </c>
+      <c r="S17">
+        <v>1.44</v>
+      </c>
+      <c r="T17">
+        <v>2.5</v>
+      </c>
+      <c r="U17">
         <v>2.9</v>
       </c>
-      <c r="Q17">
-        <v>2.7</v>
-      </c>
-      <c r="R17">
-        <v>2.1</v>
-      </c>
-      <c r="S17">
-        <v>1.36</v>
-      </c>
-      <c r="T17">
-        <v>2.78</v>
-      </c>
-      <c r="U17">
-        <v>2.5</v>
-      </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA17">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="AB17">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>3.81</v>
       </c>
       <c r="AD17">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R18">
+        <v>2.38</v>
+      </c>
+      <c r="S18">
+        <v>1.29</v>
+      </c>
+      <c r="T18">
+        <v>3.1</v>
+      </c>
+      <c r="U18">
+        <v>2.59</v>
+      </c>
+      <c r="V18">
+        <v>1.47</v>
+      </c>
+      <c r="W18">
+        <v>1.11</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>4.01</v>
+      </c>
+      <c r="AA18">
+        <v>1.68</v>
+      </c>
+      <c r="AB18">
+        <v>2.06</v>
+      </c>
+      <c r="AC18">
+        <v>2.62</v>
+      </c>
+      <c r="AD18">
+        <v>1.38</v>
+      </c>
+      <c r="AE18">
+        <v>1.11</v>
+      </c>
+      <c r="AF18">
+        <v>1.65</v>
+      </c>
+      <c r="AG18">
+        <v>2.05</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.22</v>
+      </c>
+      <c r="AK18">
         <v>2.1</v>
-      </c>
-      <c r="S18">
-        <v>1.38</v>
-      </c>
-      <c r="T18">
-        <v>2.7</v>
-      </c>
-      <c r="U18">
-        <v>2.7</v>
-      </c>
-      <c r="V18">
-        <v>1.35</v>
-      </c>
-      <c r="W18">
-        <v>1.08</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.27</v>
-      </c>
-      <c r="Z18">
-        <v>3.39</v>
-      </c>
-      <c r="AA18">
-        <v>1.93</v>
-      </c>
-      <c r="AB18">
-        <v>1.78</v>
-      </c>
-      <c r="AC18">
-        <v>3.2</v>
-      </c>
-      <c r="AD18">
-        <v>1.26</v>
-      </c>
-      <c r="AE18">
-        <v>1.06</v>
-      </c>
-      <c r="AF18">
-        <v>1.77</v>
-      </c>
-      <c r="AG18">
-        <v>1.89</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.24</v>
-      </c>
-      <c r="AK18">
-        <v>1.74</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="O3">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R3">
         <v>2.39</v>
@@ -819,10 +819,10 @@
         <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
         <v>1.1</v>
@@ -849,7 +849,7 @@
         <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
         <v>1.53</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
         <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="R5">
         <v>2.12</v>
@@ -1142,10 +1142,10 @@
         <v>1.37</v>
       </c>
       <c r="T5">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="U5">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="V5">
         <v>1.38</v>
@@ -1172,7 +1172,7 @@
         <v>3.08</v>
       </c>
       <c r="AD5">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
         <v>1.06</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z15">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="AA15">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC15">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
         <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.39</v>
+        <v>2.83</v>
       </c>
       <c r="AA16">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AB16">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>3.2</v>
+        <v>3.81</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AG16">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q17">
+        <v>2.26</v>
+      </c>
+      <c r="R17">
         <v>2.38</v>
       </c>
-      <c r="R17">
-        <v>2.01</v>
-      </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.59</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>2.83</v>
+        <v>4.01</v>
       </c>
       <c r="AA17">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AC17">
-        <v>3.81</v>
+        <v>2.62</v>
       </c>
       <c r="AD17">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q18">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="U18">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="AA18">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB18">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC18">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD18">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="U17">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="AA17">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB17">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC17">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="R18">
+        <v>2.38</v>
+      </c>
+      <c r="S18">
+        <v>1.29</v>
+      </c>
+      <c r="T18">
+        <v>3.1</v>
+      </c>
+      <c r="U18">
+        <v>2.59</v>
+      </c>
+      <c r="V18">
+        <v>1.47</v>
+      </c>
+      <c r="W18">
+        <v>1.11</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>4.01</v>
+      </c>
+      <c r="AA18">
+        <v>1.68</v>
+      </c>
+      <c r="AB18">
+        <v>2.06</v>
+      </c>
+      <c r="AC18">
+        <v>2.62</v>
+      </c>
+      <c r="AD18">
+        <v>1.38</v>
+      </c>
+      <c r="AE18">
+        <v>1.11</v>
+      </c>
+      <c r="AF18">
+        <v>1.65</v>
+      </c>
+      <c r="AG18">
+        <v>2.05</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.22</v>
+      </c>
+      <c r="AK18">
         <v>2.1</v>
-      </c>
-      <c r="S18">
-        <v>1.36</v>
-      </c>
-      <c r="T18">
-        <v>2.78</v>
-      </c>
-      <c r="U18">
-        <v>2.5</v>
-      </c>
-      <c r="V18">
-        <v>1.4</v>
-      </c>
-      <c r="W18">
-        <v>1.06</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.25</v>
-      </c>
-      <c r="Z18">
-        <v>3.74</v>
-      </c>
-      <c r="AA18">
-        <v>1.83</v>
-      </c>
-      <c r="AB18">
-        <v>1.95</v>
-      </c>
-      <c r="AC18">
-        <v>2.88</v>
-      </c>
-      <c r="AD18">
-        <v>1.32</v>
-      </c>
-      <c r="AE18">
-        <v>1.08</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.15</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.27</v>
-      </c>
-      <c r="AK18">
-        <v>1.51</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
         <v>3.11</v>
       </c>
       <c r="P19">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="Q19">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S19">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U19">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="V19">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W19">
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y19">
         <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AA19">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AB19">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC19">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="AD19">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>2.15</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G28">

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -810,7 +810,7 @@
         <v>2.64</v>
       </c>
       <c r="R3">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.28</v>
@@ -849,13 +849,13 @@
         <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
         <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.23</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="Q16">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="R16">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
+        <v>2.78</v>
+      </c>
+      <c r="U16">
         <v>2.5</v>
       </c>
-      <c r="U16">
-        <v>2.9</v>
-      </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>2.83</v>
+        <v>3.74</v>
       </c>
       <c r="AA16">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AB16">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
-        <v>3.81</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="R17">
+        <v>2.38</v>
+      </c>
+      <c r="S17">
+        <v>1.29</v>
+      </c>
+      <c r="T17">
+        <v>3.1</v>
+      </c>
+      <c r="U17">
+        <v>2.59</v>
+      </c>
+      <c r="V17">
+        <v>1.47</v>
+      </c>
+      <c r="W17">
+        <v>1.11</v>
+      </c>
+      <c r="X17">
+        <v>1.03</v>
+      </c>
+      <c r="Y17">
+        <v>1.22</v>
+      </c>
+      <c r="Z17">
+        <v>4.01</v>
+      </c>
+      <c r="AA17">
+        <v>1.68</v>
+      </c>
+      <c r="AB17">
+        <v>2.06</v>
+      </c>
+      <c r="AC17">
+        <v>2.62</v>
+      </c>
+      <c r="AD17">
+        <v>1.38</v>
+      </c>
+      <c r="AE17">
+        <v>1.11</v>
+      </c>
+      <c r="AF17">
+        <v>1.65</v>
+      </c>
+      <c r="AG17">
+        <v>2.05</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.22</v>
+      </c>
+      <c r="AK17">
         <v>2.1</v>
-      </c>
-      <c r="S17">
-        <v>1.36</v>
-      </c>
-      <c r="T17">
-        <v>2.78</v>
-      </c>
-      <c r="U17">
-        <v>2.5</v>
-      </c>
-      <c r="V17">
-        <v>1.4</v>
-      </c>
-      <c r="W17">
-        <v>1.06</v>
-      </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>1.25</v>
-      </c>
-      <c r="Z17">
-        <v>3.74</v>
-      </c>
-      <c r="AA17">
-        <v>1.83</v>
-      </c>
-      <c r="AB17">
-        <v>1.95</v>
-      </c>
-      <c r="AC17">
-        <v>2.88</v>
-      </c>
-      <c r="AD17">
-        <v>1.32</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
-      <c r="AF17">
-        <v>1.62</v>
-      </c>
-      <c r="AG17">
-        <v>2.15</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.27</v>
-      </c>
-      <c r="AK17">
-        <v>1.51</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q18">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="S18">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>4.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA18">
+        <v>2.09</v>
+      </c>
+      <c r="AB18">
         <v>1.68</v>
       </c>
-      <c r="AB18">
-        <v>2.06</v>
-      </c>
       <c r="AC18">
-        <v>2.62</v>
+        <v>3.81</v>
       </c>
       <c r="AD18">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK18">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -1127,62 +1127,62 @@
         <v>3.55</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
+        <v>1.38</v>
+      </c>
+      <c r="T5">
+        <v>2.77</v>
+      </c>
+      <c r="U5">
+        <v>2.93</v>
+      </c>
+      <c r="V5">
         <v>1.37</v>
-      </c>
-      <c r="T5">
-        <v>2.98</v>
-      </c>
-      <c r="U5">
-        <v>2.86</v>
-      </c>
-      <c r="V5">
-        <v>1.38</v>
       </c>
       <c r="W5">
         <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB5">
+        <v>1.85</v>
+      </c>
+      <c r="AC5">
+        <v>3.4</v>
+      </c>
+      <c r="AD5">
+        <v>1.29</v>
+      </c>
+      <c r="AE5">
+        <v>1.1</v>
+      </c>
+      <c r="AF5">
+        <v>1.8</v>
+      </c>
+      <c r="AG5">
         <v>1.9</v>
       </c>
-      <c r="AC5">
-        <v>3.08</v>
-      </c>
-      <c r="AD5">
-        <v>1.31</v>
-      </c>
-      <c r="AE5">
-        <v>1.06</v>
-      </c>
-      <c r="AF5">
-        <v>1.78</v>
-      </c>
-      <c r="AG5">
-        <v>1.93</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.87</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q6">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
         <v>1.91</v>
       </c>
       <c r="S6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T6">
         <v>2.39</v>
@@ -1320,10 +1320,10 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z6">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AA6">
         <v>2.46</v>
@@ -1332,19 +1332,19 @@
         <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="AD6">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE6">
         <v>1</v>
       </c>
       <c r="AF6">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AG6">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>9.4</v>
+        <v>8.35</v>
       </c>
       <c r="O9">
-        <v>6.31</v>
+        <v>6.1</v>
       </c>
       <c r="P9">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Q9">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R9">
         <v>2.7</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="U9">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
         <v>1.13</v>
@@ -1812,16 +1812,16 @@
         <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="AA9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB9">
         <v>2.46</v>
       </c>
       <c r="AC9">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AD9">
         <v>1.6</v>
@@ -1833,7 +1833,7 @@
         <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2268,13 +2268,13 @@
         <v>3.35</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="Q12">
-        <v>4.32</v>
+        <v>4.15</v>
       </c>
       <c r="R12">
         <v>1.95</v>
@@ -2286,19 +2286,19 @@
         <v>2.5</v>
       </c>
       <c r="U12">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z12">
         <v>3.03</v>
@@ -2307,23 +2307,23 @@
         <v>2.11</v>
       </c>
       <c r="AB12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
         <v>1.03</v>
       </c>
       <c r="AF12">
+        <v>1.8</v>
+      </c>
+      <c r="AG12">
         <v>1.85</v>
       </c>
-      <c r="AG12">
-        <v>1.81</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK12">
         <v>1.25</v>
@@ -2763,10 +2763,10 @@
         <v>3.75</v>
       </c>
       <c r="Q15">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
         <v>1.38</v>
@@ -2778,10 +2778,10 @@
         <v>2.7</v>
       </c>
       <c r="V15">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2790,10 +2790,10 @@
         <v>1.27</v>
       </c>
       <c r="Z15">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
       <c r="AA15">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB15">
         <v>1.78</v>
@@ -2811,7 +2811,7 @@
         <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
         <v>1.74</v>
@@ -2926,16 +2926,16 @@
         <v>2.9</v>
       </c>
       <c r="Q16">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
         <v>2.5</v>
@@ -2944,7 +2944,7 @@
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2956,16 +2956,16 @@
         <v>3.74</v>
       </c>
       <c r="AA16">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD16">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
         <v>1.08</v>
@@ -2974,7 +2974,7 @@
         <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK16">
         <v>1.51</v>
@@ -3098,13 +3098,13 @@
         <v>1.29</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
         <v>1.11</v>
@@ -3137,23 +3137,23 @@
         <v>1.65</v>
       </c>
       <c r="AG17">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.25</v>
+      </c>
+      <c r="AK17">
         <v>2.05</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.22</v>
-      </c>
-      <c r="AK17">
-        <v>2.1</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>1.74</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q18">
         <v>2.38</v>
@@ -3264,13 +3264,13 @@
         <v>2.5</v>
       </c>
       <c r="U18">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
         <v>1.03</v>
@@ -3288,7 +3288,7 @@
         <v>1.68</v>
       </c>
       <c r="AC18">
-        <v>3.81</v>
+        <v>3.58</v>
       </c>
       <c r="AD18">
         <v>1.21</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O19">
         <v>3.11</v>
@@ -3421,31 +3421,31 @@
         <v>1.91</v>
       </c>
       <c r="S19">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U19">
         <v>4.1</v>
       </c>
       <c r="V19">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W19">
         <v>1.01</v>
       </c>
       <c r="X19">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
         <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AA19">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB19">
         <v>1.48</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P20">
-        <v>3.05</v>
+        <v>2.69</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
         <v>2.15</v>
@@ -3587,7 +3587,7 @@
         <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
         <v>2.88</v>
@@ -3599,28 +3599,28 @@
         <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB20">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="AD20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
         <v>1.75</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
         <v>3.35</v>
@@ -1163,16 +1163,16 @@
         <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB5">
         <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD5">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>3.05</v>
@@ -1305,7 +1305,7 @@
         <v>1.51</v>
       </c>
       <c r="T6">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="U6">
         <v>3.42</v>
@@ -1326,13 +1326,13 @@
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AB6">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AC6">
-        <v>4.66</v>
+        <v>4.55</v>
       </c>
       <c r="AD6">
         <v>1.13</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G24">
@@ -4324,658 +4324,6 @@
         <v>0</v>
       </c>
       <c r="AU24" t="inlineStr">
-        <is>
-          <t>2026-08-20 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Qabala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Safa</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-08-20 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Turan</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>İnter Bakı</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-08-20 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Sabah</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Sumqayıt</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-08-20 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Azerbaijan Premyer Liqası</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Zira</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Mil Mugan FK</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-08-20 21:00:00</t>
         </is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -810,16 +810,16 @@
         <v>2.64</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
         <v>1.28</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="U3">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="V3">
         <v>1.5</v>
@@ -834,7 +834,7 @@
         <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA3">
         <v>1.62</v>
@@ -846,13 +846,13 @@
         <v>2.5</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE3">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
         <v>2.32</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>3.35</v>
@@ -1133,19 +1133,19 @@
         <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>4.6</v>
+        <v>3.87</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
         <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="V5">
         <v>1.37</v>
@@ -1154,10 +1154,10 @@
         <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
         <v>3.2</v>
@@ -1166,10 +1166,10 @@
         <v>1.96</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD5">
         <v>1.26</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="O6">
         <v>3.05</v>
@@ -1299,13 +1299,13 @@
         <v>3.35</v>
       </c>
       <c r="R6">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S6">
         <v>1.51</v>
       </c>
       <c r="T6">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="U6">
         <v>3.42</v>
@@ -1320,13 +1320,13 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z6">
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AB6">
         <v>1.53</v>
@@ -1344,7 +1344,7 @@
         <v>1.99</v>
       </c>
       <c r="AG6">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK6">
         <v>1.46</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>8.35</v>
+        <v>9.4</v>
       </c>
       <c r="O9">
-        <v>6.1</v>
+        <v>6.31</v>
       </c>
       <c r="P9">
         <v>1.21</v>
       </c>
       <c r="Q9">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="S9">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T9">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="U9">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V9">
         <v>1.65</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z9">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AA9">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB9">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AC9">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AD9">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE9">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.12</v>
+        <v>3.6</v>
       </c>
       <c r="AK9">
         <v>1.03</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O19">
         <v>3.11</v>
       </c>
       <c r="P19">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>3.09</v>
       </c>
       <c r="R19">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S19">
         <v>1.5</v>
@@ -3427,10 +3427,10 @@
         <v>2.4</v>
       </c>
       <c r="U19">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="V19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W19">
         <v>1.01</v>
@@ -3439,31 +3439,31 @@
         <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AA19">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AB19">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AG19">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P22">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3916,7 +3916,7 @@
         <v>2.88</v>
       </c>
       <c r="U22">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="V22">
         <v>1.38</v>
@@ -3925,19 +3925,19 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z22">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB22">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC22">
         <v>3.8</v>
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG22">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
         <v>2.38</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
         <v>3.25</v>
       </c>
       <c r="P12">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="Q12">
         <v>4.15</v>
       </c>
       <c r="R12">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
         <v>1.44</v>
@@ -2307,10 +2307,10 @@
         <v>2.11</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>3.72</v>
+        <v>3.86</v>
       </c>
       <c r="AD12">
         <v>1.2</v>
@@ -2319,7 +2319,7 @@
         <v>1.03</v>
       </c>
       <c r="AF12">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
         <v>1.85</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AK12">
         <v>1.25</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
         <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="R15">
         <v>2.05</v>
@@ -2772,46 +2772,46 @@
         <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="U15">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA15">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB15">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC15">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG15">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
         <v>2.9</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S16">
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
         <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC16">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD16">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.36</v>
       </c>
       <c r="AK16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3092,22 +3092,22 @@
         <v>2.26</v>
       </c>
       <c r="R17">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U17">
         <v>2.47</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3125,10 +3125,10 @@
         <v>2.06</v>
       </c>
       <c r="AC17">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AD17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
         <v>1.11</v>
@@ -3137,7 +3137,7 @@
         <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="O18">
         <v>3.45</v>
@@ -3252,10 +3252,10 @@
         <v>4</v>
       </c>
       <c r="Q18">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R18">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="S18">
         <v>1.44</v>
@@ -3264,25 +3264,25 @@
         <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V18">
         <v>1.31</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="AA18">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AB18">
         <v>1.68</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3.11</v>
+        <v>3.06</v>
       </c>
       <c r="P19">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>3.09</v>
+        <v>2.76</v>
       </c>
       <c r="R19">
         <v>1.98</v>
@@ -3442,7 +3442,7 @@
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AA19">
         <v>2.63</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,25 +3569,25 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="P20">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
         <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U20">
         <v>2.88</v>
@@ -3596,34 +3596,34 @@
         <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
         <v>3.3</v>
       </c>
       <c r="AA20">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB20">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="AD20">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
         <v>2</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
         <v>1.5</v>
@@ -3741,55 +3741,55 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O22">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P22">
         <v>5.5</v>
@@ -3916,7 +3916,7 @@
         <v>2.88</v>
       </c>
       <c r="U22">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="V22">
         <v>1.38</v>
@@ -3940,16 +3940,16 @@
         <v>1.77</v>
       </c>
       <c r="AC22">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AG22">
         <v>1.65</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK22">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="O3">
         <v>3.5</v>
       </c>
       <c r="P3">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="Q3">
         <v>2.64</v>
@@ -852,10 +852,10 @@
         <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="U15">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="AA15">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AB15">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="AC15">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="AD15">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>2.47</v>
+        <v>3.2</v>
       </c>
       <c r="V17">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>4.01</v>
+        <v>3.01</v>
       </c>
       <c r="AA17">
+        <v>2.14</v>
+      </c>
+      <c r="AB17">
         <v>1.68</v>
       </c>
-      <c r="AB17">
-        <v>2.06</v>
-      </c>
       <c r="AC17">
-        <v>2.82</v>
+        <v>3.58</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="R18">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="U18">
+        <v>2.92</v>
+      </c>
+      <c r="V18">
+        <v>1.38</v>
+      </c>
+      <c r="W18">
+        <v>1.04</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.26</v>
+      </c>
+      <c r="Z18">
         <v>3.2</v>
       </c>
-      <c r="V18">
-        <v>1.31</v>
-      </c>
-      <c r="W18">
-        <v>1.03</v>
-      </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.36</v>
-      </c>
-      <c r="Z18">
-        <v>3.01</v>
-      </c>
       <c r="AA18">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
+        <v>1.92</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.19</v>
+      </c>
+      <c r="AK18">
         <v>1.75</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.25</v>
-      </c>
-      <c r="AK18">
-        <v>2</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q5">
-        <v>3.87</v>
+        <v>4.65</v>
       </c>
       <c r="R5">
         <v>2.08</v>
@@ -1145,10 +1145,10 @@
         <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
         <v>1.04</v>
@@ -1175,7 +1175,7 @@
         <v>1.26</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
         <v>1.8</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="Q6">
         <v>3.35</v>
       </c>
       <c r="R6">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="S6">
         <v>1.51</v>
@@ -1326,7 +1326,7 @@
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AB6">
         <v>1.53</v>
@@ -1360,7 +1360,7 @@
         <v>1.33</v>
       </c>
       <c r="AK6">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="O9">
         <v>6.31</v>
@@ -1785,10 +1785,10 @@
         <v>1.21</v>
       </c>
       <c r="Q9">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R9">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S9">
         <v>1.19</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB9">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AC9">
         <v>2.17</v>
       </c>
       <c r="AD9">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE9">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O12">
         <v>3.25</v>
@@ -2277,13 +2277,13 @@
         <v>4.15</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U12">
         <v>3.08</v>
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R15">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2787,7 +2787,7 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
         <v>4.01</v>
@@ -2802,7 +2802,7 @@
         <v>2.82</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P16">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q16">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U16">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB16">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC16">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="O17">
         <v>3.45</v>
@@ -3089,7 +3089,7 @@
         <v>4</v>
       </c>
       <c r="Q17">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="R17">
         <v>2.16</v>
@@ -3119,10 +3119,10 @@
         <v>3.01</v>
       </c>
       <c r="AA17">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
         <v>3.58</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
         <v>2</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q18">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA18">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB18">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC18">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG18">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AK18">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>3.06</v>
       </c>
       <c r="P19">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q19">
         <v>2.76</v>
@@ -3442,10 +3442,10 @@
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA19">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AB19">
         <v>1.44</v>
@@ -3457,7 +3457,7 @@
         <v>1.14</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
         <v>2.17</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="O20">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q20">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
         <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3642,7 +3642,7 @@
         <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R21">
         <v>2.05</v>
@@ -3750,25 +3750,25 @@
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
         <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z21">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AA21">
         <v>2.25</v>
@@ -3777,13 +3777,13 @@
         <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>4.24</v>
+        <v>3.98</v>
       </c>
       <c r="AD21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
         <v>1.91</v>
@@ -3904,7 +3904,7 @@
         <v>5.5</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R22">
         <v>2.25</v>
@@ -3925,7 +3925,7 @@
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.31</v>
@@ -3934,7 +3934,7 @@
         <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
         <v>1.77</v>
@@ -3949,10 +3949,10 @@
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="O16">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P16">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q16">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="R16">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
+        <v>1.31</v>
+      </c>
+      <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
         <v>1.36</v>
       </c>
-      <c r="W16">
+      <c r="Z16">
+        <v>3.01</v>
+      </c>
+      <c r="AA16">
+        <v>2.09</v>
+      </c>
+      <c r="AB16">
+        <v>1.66</v>
+      </c>
+      <c r="AC16">
+        <v>3.58</v>
+      </c>
+      <c r="AD16">
+        <v>1.21</v>
+      </c>
+      <c r="AE16">
         <v>1.04</v>
       </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
-        <v>1.26</v>
-      </c>
-      <c r="Z16">
-        <v>3.4</v>
-      </c>
-      <c r="AA16">
-        <v>1.92</v>
-      </c>
-      <c r="AB16">
-        <v>1.79</v>
-      </c>
-      <c r="AC16">
-        <v>3.2</v>
-      </c>
-      <c r="AD16">
-        <v>1.26</v>
-      </c>
-      <c r="AE16">
-        <v>1.06</v>
-      </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="R17">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
+        <v>1.4</v>
+      </c>
+      <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.23</v>
+      </c>
+      <c r="Z17">
+        <v>3.42</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.85</v>
+      </c>
+      <c r="AC17">
+        <v>3.05</v>
+      </c>
+      <c r="AD17">
+        <v>1.28</v>
+      </c>
+      <c r="AE17">
+        <v>1.07</v>
+      </c>
+      <c r="AF17">
+        <v>1.65</v>
+      </c>
+      <c r="AG17">
+        <v>2.08</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.31</v>
       </c>
-      <c r="W17">
-        <v>1.03</v>
-      </c>
-      <c r="X17">
-        <v>1.03</v>
-      </c>
-      <c r="Y17">
-        <v>1.36</v>
-      </c>
-      <c r="Z17">
-        <v>3.01</v>
-      </c>
-      <c r="AA17">
-        <v>2.09</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.58</v>
-      </c>
-      <c r="AD17">
-        <v>1.21</v>
-      </c>
-      <c r="AE17">
-        <v>1.04</v>
-      </c>
-      <c r="AF17">
-        <v>1.94</v>
-      </c>
-      <c r="AG17">
-        <v>1.75</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.19</v>
-      </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P18">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q18">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="R18">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="U18">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA18">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="Q3">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
         <v>1.28</v>
       </c>
       <c r="T3">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W3">
         <v>1.1</v>
@@ -834,25 +834,25 @@
         <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB3">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC3">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD3">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
         <v>2.38</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>8.4</v>
+        <v>11.1</v>
       </c>
       <c r="O9">
-        <v>6.31</v>
+        <v>7.01</v>
       </c>
       <c r="P9">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Q9">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V9">
         <v>1.65</v>
@@ -1812,19 +1812,19 @@
         <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="AA9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB9">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
       <c r="AC9">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD9">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE9">
         <v>1.25</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AK9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O5">
         <v>3.4</v>
@@ -1139,13 +1139,13 @@
         <v>2.08</v>
       </c>
       <c r="S5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
         <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="V5">
         <v>1.38</v>
@@ -1197,7 +1197,7 @@
         <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -1296,7 +1296,7 @@
         <v>2.56</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="R6">
         <v>1.89</v>
@@ -1326,7 +1326,7 @@
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB6">
         <v>1.53</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
         <v>1.37</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
         <v>3.25</v>
@@ -2277,19 +2277,19 @@
         <v>4.15</v>
       </c>
       <c r="R12">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2301,7 +2301,7 @@
         <v>1.35</v>
       </c>
       <c r="Z12">
-        <v>3.03</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
         <v>2.11</v>
@@ -2310,7 +2310,7 @@
         <v>1.67</v>
       </c>
       <c r="AC12">
-        <v>3.86</v>
+        <v>3.72</v>
       </c>
       <c r="AD12">
         <v>1.2</v>
@@ -2322,7 +2322,7 @@
         <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2778,7 +2778,7 @@
         <v>2.47</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2790,7 +2790,7 @@
         <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>4.01</v>
+        <v>3.92</v>
       </c>
       <c r="AA15">
         <v>1.68</v>
@@ -2802,7 +2802,7 @@
         <v>2.82</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
         <v>1.11</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
         <v>1.94</v>
@@ -2920,16 +2920,16 @@
         <v>1.74</v>
       </c>
       <c r="O16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
         <v>4</v>
       </c>
       <c r="Q16">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
         <v>1.44</v>
@@ -2938,7 +2938,7 @@
         <v>2.5</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="V16">
         <v>1.31</v>
@@ -2950,19 +2950,19 @@
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="AA16">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="AB16">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
       <c r="AD16">
         <v>1.21</v>
@@ -3089,28 +3089,28 @@
         <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
         <v>2.7</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.23</v>
@@ -3119,10 +3119,10 @@
         <v>3.42</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC17">
         <v>3.05</v>
@@ -3131,10 +3131,10 @@
         <v>1.28</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
         <v>2.08</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
         <v>1.5</v>
@@ -3252,10 +3252,10 @@
         <v>3.8</v>
       </c>
       <c r="Q18">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S18">
         <v>1.38</v>
@@ -3264,10 +3264,10 @@
         <v>2.93</v>
       </c>
       <c r="U18">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
         <v>1.04</v>
@@ -3297,7 +3297,7 @@
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG18">
         <v>1.92</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
         <v>1.83</v>
@@ -3409,16 +3409,16 @@
         <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="P19">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="R19">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="S19">
         <v>1.5</v>
@@ -3442,28 +3442,28 @@
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA19">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AB19">
         <v>1.44</v>
       </c>
       <c r="AC19">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AG19">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -3584,16 +3584,16 @@
         <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="U20">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V20">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3605,10 +3605,10 @@
         <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.3</v>
+        <v>3.49</v>
       </c>
       <c r="AA20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB20">
         <v>1.81</v>
@@ -3623,7 +3623,7 @@
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
         <v>2</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,34 +3741,34 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S21">
         <v>1.4</v>
       </c>
       <c r="T21">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="U21">
         <v>3.16</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W21">
         <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
         <v>1.4</v>
       </c>
       <c r="Z21">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="AA21">
         <v>2.25</v>
@@ -3777,19 +3777,19 @@
         <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>3.98</v>
+        <v>4.24</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG21">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
         <v>1.52</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O22">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P22">
         <v>5.5</v>
@@ -3910,49 +3910,49 @@
         <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T22">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U22">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z22">
         <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB22">
         <v>1.77</v>
       </c>
       <c r="AC22">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O19">
         <v>2.95</v>
@@ -3415,13 +3415,13 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R19">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T19">
         <v>2.4</v>
@@ -3454,7 +3454,7 @@
         <v>5.3</v>
       </c>
       <c r="AD19">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
         <v>1.04</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -3741,34 +3741,34 @@
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S21">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T21">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U21">
         <v>3.16</v>
       </c>
       <c r="V21">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
         <v>1.4</v>
       </c>
       <c r="Z21">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA21">
         <v>2.25</v>
@@ -3777,7 +3777,7 @@
         <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
@@ -3805,7 +3805,7 @@
         <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>1.5</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P22">
         <v>5.5</v>
@@ -3907,19 +3907,19 @@
         <v>2.05</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U22">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
         <v>1.07</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA22">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB22">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AD22">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -801,10 +801,10 @@
         <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -813,19 +813,19 @@
         <v>2.38</v>
       </c>
       <c r="S3">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U3">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V3">
         <v>1.53</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -843,7 +843,7 @@
         <v>2.3</v>
       </c>
       <c r="AC3">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AD3">
         <v>1.44</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="O5">
         <v>3.4</v>
       </c>
       <c r="P5">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S5">
         <v>1.39</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="U5">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="V5">
         <v>1.38</v>
@@ -1157,7 +1157,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
         <v>3.2</v>
@@ -1197,7 +1197,7 @@
         <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="O6">
         <v>3</v>
@@ -1302,10 +1302,10 @@
         <v>1.89</v>
       </c>
       <c r="S6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="U6">
         <v>3.42</v>
@@ -1320,19 +1320,19 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z6">
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AB6">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>4.55</v>
+        <v>4.66</v>
       </c>
       <c r="AD6">
         <v>1.13</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AK6">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>11.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O9">
-        <v>7.01</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>1.23</v>
@@ -1788,7 +1788,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S9">
         <v>1.22</v>
@@ -1797,13 +1797,13 @@
         <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V9">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,28 +1812,28 @@
         <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>5.33</v>
+        <v>5.45</v>
       </c>
       <c r="AA9">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AB9">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AC9">
         <v>2.1</v>
       </c>
       <c r="AD9">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE9">
         <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG9">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AK9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,49 +2265,49 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q12">
-        <v>4.15</v>
+        <v>3.73</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S12">
         <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U12">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z12">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA12">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AB12">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
         <v>3.72</v>
@@ -2316,13 +2316,13 @@
         <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
         <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2763,22 +2763,22 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R15">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T15">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
         <v>1.68</v>
@@ -2799,35 +2799,35 @@
         <v>2.06</v>
       </c>
       <c r="AC15">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
         <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
         <v>1.65</v>
       </c>
       <c r="AG15">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.25</v>
+      </c>
+      <c r="AK15">
         <v>2.05</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.22</v>
-      </c>
-      <c r="AK15">
-        <v>1.94</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
         <v>4</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R16">
         <v>2.1</v>
@@ -2938,40 +2938,40 @@
         <v>2.5</v>
       </c>
       <c r="U16">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="V16">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
         <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AA16">
         <v>2.14</v>
       </c>
       <c r="AB16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC16">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="AD16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG16">
         <v>1.75</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
+        <v>2.96</v>
+      </c>
+      <c r="R17">
+        <v>2.1</v>
+      </c>
+      <c r="S17">
+        <v>1.39</v>
+      </c>
+      <c r="T17">
         <v>2.7</v>
       </c>
-      <c r="R17">
-        <v>2</v>
-      </c>
-      <c r="S17">
-        <v>1.38</v>
-      </c>
-      <c r="T17">
-        <v>2.9</v>
-      </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB17">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AC17">
         <v>3.05</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -3270,7 +3270,7 @@
         <v>1.38</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3288,10 +3288,10 @@
         <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
@@ -3300,7 +3300,7 @@
         <v>1.77</v>
       </c>
       <c r="AG18">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="O19">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="P19">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
       </c>
       <c r="R19">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="U19">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W19">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA19">
         <v>2.63</v>
@@ -3451,7 +3451,7 @@
         <v>1.44</v>
       </c>
       <c r="AC19">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD19">
         <v>1.14</v>
@@ -3460,10 +3460,10 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AG19">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
         <v>1.57</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="Q20">
         <v>3.1</v>
@@ -3584,13 +3584,13 @@
         <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
         <v>2.94</v>
       </c>
       <c r="U20">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
         <v>1.4</v>
@@ -3599,16 +3599,16 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
         <v>1.81</v>
@@ -3620,7 +3620,7 @@
         <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
         <v>1.43</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -635,43 +635,43 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA2">
         <v>2.1</v>
@@ -680,19 +680,19 @@
         <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>3.3</v>
+      </c>
+      <c r="O4">
+        <v>3.35</v>
+      </c>
+      <c r="P4">
+        <v>1.93</v>
+      </c>
+      <c r="Q4">
+        <v>4</v>
+      </c>
+      <c r="R4">
+        <v>2.2</v>
+      </c>
+      <c r="S4">
+        <v>1.35</v>
+      </c>
+      <c r="T4">
+        <v>2.79</v>
+      </c>
+      <c r="U4">
+        <v>2.62</v>
+      </c>
+      <c r="V4">
+        <v>1.4</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.24</v>
+      </c>
+      <c r="Z4">
         <v>3.5</v>
       </c>
-      <c r="O4">
-        <v>3.3</v>
-      </c>
-      <c r="P4">
-        <v>1.94</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
       <c r="AA4">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AB4">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1142,10 +1142,10 @@
         <v>1.39</v>
       </c>
       <c r="T5">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="V5">
         <v>1.38</v>
@@ -1163,13 +1163,13 @@
         <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC5">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD5">
         <v>1.26</v>
@@ -1197,7 +1197,7 @@
         <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="Q6">
         <v>3.12</v>
@@ -1305,7 +1305,7 @@
         <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="U6">
         <v>3.42</v>
@@ -1326,13 +1326,13 @@
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB6">
         <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>4.66</v>
+        <v>4.72</v>
       </c>
       <c r="AD6">
         <v>1.13</v>
@@ -2271,7 +2271,7 @@
         <v>3.1</v>
       </c>
       <c r="P12">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="Q12">
         <v>3.73</v>
@@ -2283,13 +2283,13 @@
         <v>1.44</v>
       </c>
       <c r="T12">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
         <v>1.04</v>
@@ -2304,7 +2304,7 @@
         <v>2.9</v>
       </c>
       <c r="AA12">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB12">
         <v>1.65</v>
@@ -2775,7 +2775,7 @@
         <v>3.3</v>
       </c>
       <c r="U15">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V15">
         <v>1.5</v>
@@ -2793,10 +2793,10 @@
         <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB15">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
         <v>2.75</v>
@@ -2811,7 +2811,7 @@
         <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U16">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V16">
         <v>1.35</v>
@@ -2956,7 +2956,7 @@
         <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
         <v>1.67</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
         <v>1.87</v>
@@ -3119,16 +3119,16 @@
         <v>3.6</v>
       </c>
       <c r="AA17">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB17">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD17">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
@@ -3137,7 +3137,7 @@
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3261,10 +3261,10 @@
         <v>1.38</v>
       </c>
       <c r="T18">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="U18">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="V18">
         <v>1.38</v>
@@ -3279,7 +3279,7 @@
         <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA18">
         <v>1.92</v>
@@ -3288,7 +3288,7 @@
         <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD18">
         <v>1.29</v>
@@ -3750,7 +3750,7 @@
         <v>1.48</v>
       </c>
       <c r="T21">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="U21">
         <v>3.16</v>
@@ -3759,7 +3759,7 @@
         <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
         <v>1.08</v>
@@ -3780,7 +3780,7 @@
         <v>4.33</v>
       </c>
       <c r="AD21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
         <v>1.57</v>
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>6.18</v>
       </c>
       <c r="Q22">
         <v>2.05</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3919,7 +3919,7 @@
         <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W22">
         <v>1.07</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z22">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC22">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
         <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P2">
         <v>2.31</v>
@@ -677,13 +677,13 @@
         <v>2.1</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC2">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
         <v>1.03</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
         <v>3.35</v>
       </c>
       <c r="P4">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
         <v>2.79</v>
@@ -1009,16 +1009,16 @@
         <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.68</v>
       </c>
       <c r="AK4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -650,16 +650,16 @@
         <v>1.97</v>
       </c>
       <c r="S2">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
         <v>2.56</v>
       </c>
       <c r="U2">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="V2">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
         <v>1.04</v>
@@ -674,7 +674,7 @@
         <v>2.91</v>
       </c>
       <c r="AA2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB2">
         <v>1.69</v>
@@ -801,10 +801,10 @@
         <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="Q3">
         <v>2.5</v>
@@ -813,7 +813,7 @@
         <v>2.38</v>
       </c>
       <c r="S3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T3">
         <v>3.4</v>
@@ -822,10 +822,10 @@
         <v>2.38</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -834,7 +834,7 @@
         <v>1.16</v>
       </c>
       <c r="Z3">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA3">
         <v>1.61</v>
@@ -843,19 +843,19 @@
         <v>2.3</v>
       </c>
       <c r="AC3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AD3">
         <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF3">
         <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>3.35</v>
       </c>
       <c r="P4">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
         <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <v>2.62</v>
@@ -1009,7 +1009,7 @@
         <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
@@ -1018,7 +1018,7 @@
         <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
         <v>1.25</v>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
         <v>3.4</v>
@@ -1136,7 +1136,7 @@
         <v>4.67</v>
       </c>
       <c r="R5">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S5">
         <v>1.39</v>
@@ -1160,7 +1160,7 @@
         <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="AA5">
         <v>1.9</v>
@@ -1169,7 +1169,7 @@
         <v>1.82</v>
       </c>
       <c r="AC5">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AD5">
         <v>1.26</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>3.05</v>
@@ -1296,7 +1296,7 @@
         <v>2.65</v>
       </c>
       <c r="Q6">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
         <v>1.89</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>8.109999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="O9">
         <v>6</v>
@@ -1797,13 +1797,13 @@
         <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,28 +1812,28 @@
         <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AA9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB9">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC9">
         <v>2.1</v>
       </c>
       <c r="AD9">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE9">
         <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AG9">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>3.85</v>
+        <v>1.11</v>
       </c>
       <c r="AK9">
         <v>1.05</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q12">
         <v>3.73</v>
@@ -2280,19 +2280,19 @@
         <v>1.97</v>
       </c>
       <c r="S12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
         <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2301,28 +2301,28 @@
         <v>1.36</v>
       </c>
       <c r="Z12">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
         <v>2.15</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC12">
         <v>3.72</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF12">
         <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G14">
@@ -2600,55 +2600,55 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q15">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
+        <v>1.43</v>
+      </c>
+      <c r="T15">
+        <v>2.75</v>
+      </c>
+      <c r="U15">
+        <v>2.86</v>
+      </c>
+      <c r="V15">
         <v>1.31</v>
       </c>
-      <c r="T15">
-        <v>3.3</v>
-      </c>
-      <c r="U15">
-        <v>2.6</v>
-      </c>
-      <c r="V15">
-        <v>1.5</v>
-      </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="R16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T16">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="U16">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
+        <v>1.06</v>
+      </c>
+      <c r="X16">
         <v>1.03</v>
       </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AB16">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
       <c r="Q17">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U17">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.26</v>
+      </c>
+      <c r="Z17">
+        <v>3.43</v>
+      </c>
+      <c r="AA17">
+        <v>1.93</v>
+      </c>
+      <c r="AB17">
+        <v>1.79</v>
+      </c>
+      <c r="AC17">
+        <v>3.43</v>
+      </c>
+      <c r="AD17">
+        <v>1.29</v>
+      </c>
+      <c r="AE17">
         <v>1.06</v>
       </c>
-      <c r="X17">
-        <v>1.03</v>
-      </c>
-      <c r="Y17">
-        <v>1.25</v>
-      </c>
-      <c r="Z17">
-        <v>3.6</v>
-      </c>
-      <c r="AA17">
-        <v>1.82</v>
-      </c>
-      <c r="AB17">
-        <v>1.85</v>
-      </c>
-      <c r="AC17">
-        <v>3.04</v>
-      </c>
-      <c r="AD17">
-        <v>1.32</v>
-      </c>
-      <c r="AE17">
-        <v>1.07</v>
-      </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="R18">
         <v>2.15</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T18">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA18">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB18">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC18">
-        <v>3.43</v>
+        <v>2.97</v>
       </c>
       <c r="AD18">
+        <v>1.3</v>
+      </c>
+      <c r="AE18">
+        <v>1.08</v>
+      </c>
+      <c r="AF18">
+        <v>1.65</v>
+      </c>
+      <c r="AG18">
+        <v>2.1</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.29</v>
       </c>
-      <c r="AE18">
-        <v>1.06</v>
-      </c>
-      <c r="AF18">
-        <v>1.77</v>
-      </c>
-      <c r="AG18">
-        <v>1.85</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.19</v>
-      </c>
       <c r="AK18">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="Q19">
         <v>2.95</v>
@@ -3424,13 +3424,13 @@
         <v>1.63</v>
       </c>
       <c r="T19">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="U19">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="V19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W19">
         <v>1.01</v>
@@ -3442,13 +3442,13 @@
         <v>1.55</v>
       </c>
       <c r="Z19">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AA19">
         <v>2.63</v>
       </c>
       <c r="AB19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC19">
         <v>5.5</v>
@@ -3460,7 +3460,7 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AG19">
         <v>1.61</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S20">
         <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V20">
         <v>1.4</v>
@@ -3599,7 +3599,7 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.25</v>
@@ -3608,7 +3608,7 @@
         <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB20">
         <v>1.81</v>
@@ -3620,7 +3620,7 @@
         <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
         <v>1.43</v>
@@ -3750,7 +3750,7 @@
         <v>1.48</v>
       </c>
       <c r="T21">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="U21">
         <v>3.16</v>
@@ -3762,7 +3762,7 @@
         <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
         <v>1.4</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="P22">
-        <v>6.18</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
         <v>2.05</v>
@@ -3934,10 +3934,10 @@
         <v>2.92</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB22">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AC22">
         <v>3.25</v>
@@ -3946,13 +3946,13 @@
         <v>1.3</v>
       </c>
       <c r="AE22">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.08</v>
       </c>
       <c r="AK22">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -1459,55 +1459,55 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O16">
         <v>3.25</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
       <c r="Q16">
+        <v>2.4</v>
+      </c>
+      <c r="R16">
+        <v>2.06</v>
+      </c>
+      <c r="S16">
+        <v>1.38</v>
+      </c>
+      <c r="T16">
         <v>2.95</v>
       </c>
-      <c r="R16">
-        <v>2</v>
-      </c>
-      <c r="S16">
-        <v>1.39</v>
-      </c>
-      <c r="T16">
-        <v>2.71</v>
-      </c>
       <c r="U16">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
+        <v>1.08</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>1.26</v>
+      </c>
+      <c r="Z16">
+        <v>3.43</v>
+      </c>
+      <c r="AA16">
+        <v>1.93</v>
+      </c>
+      <c r="AB16">
+        <v>1.79</v>
+      </c>
+      <c r="AC16">
+        <v>3.43</v>
+      </c>
+      <c r="AD16">
+        <v>1.29</v>
+      </c>
+      <c r="AE16">
         <v>1.06</v>
       </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.23</v>
-      </c>
-      <c r="Z16">
-        <v>3.42</v>
-      </c>
-      <c r="AA16">
+      <c r="AF16">
+        <v>1.77</v>
+      </c>
+      <c r="AG16">
+        <v>1.92</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.17</v>
+      </c>
+      <c r="AK16">
         <v>1.83</v>
-      </c>
-      <c r="AB16">
-        <v>1.84</v>
-      </c>
-      <c r="AC16">
-        <v>3.05</v>
-      </c>
-      <c r="AD16">
-        <v>1.28</v>
-      </c>
-      <c r="AE16">
-        <v>1.07</v>
-      </c>
-      <c r="AF16">
-        <v>1.62</v>
-      </c>
-      <c r="AG16">
-        <v>2.05</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.28</v>
-      </c>
-      <c r="AK16">
-        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="AA17">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
-        <v>3.43</v>
+        <v>2.97</v>
       </c>
       <c r="AD17">
+        <v>1.3</v>
+      </c>
+      <c r="AE17">
+        <v>1.08</v>
+      </c>
+      <c r="AF17">
+        <v>1.65</v>
+      </c>
+      <c r="AG17">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.29</v>
       </c>
-      <c r="AE17">
-        <v>1.06</v>
-      </c>
-      <c r="AF17">
-        <v>1.77</v>
-      </c>
-      <c r="AG17">
-        <v>1.92</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.17</v>
-      </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q18">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="R18">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U18">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
         <v>1.4</v>
@@ -3273,34 +3273,34 @@
         <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA18">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB18">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC18">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK18">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="R11">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
         <v>1.33</v>
@@ -2132,34 +2132,34 @@
         <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC11">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="AD11">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AK11">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
-        <v>2.05</v>
+        <v>3.21</v>
       </c>
       <c r="Q12">
-        <v>3.73</v>
+        <v>2.7</v>
       </c>
       <c r="R12">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="V12">
         <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB12">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC12">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="AD12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG12">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="R13">
+        <v>2.25</v>
+      </c>
+      <c r="S13">
+        <v>1.31</v>
+      </c>
+      <c r="T13">
+        <v>3.3</v>
+      </c>
+      <c r="U13">
+        <v>2.59</v>
+      </c>
+      <c r="V13">
+        <v>1.5</v>
+      </c>
+      <c r="W13">
+        <v>1.07</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.22</v>
+      </c>
+      <c r="Z13">
+        <v>3.9</v>
+      </c>
+      <c r="AA13">
+        <v>1.68</v>
+      </c>
+      <c r="AB13">
+        <v>2.02</v>
+      </c>
+      <c r="AC13">
+        <v>2.75</v>
+      </c>
+      <c r="AD13">
+        <v>1.4</v>
+      </c>
+      <c r="AE13">
+        <v>1.13</v>
+      </c>
+      <c r="AF13">
+        <v>1.65</v>
+      </c>
+      <c r="AG13">
         <v>2.1</v>
       </c>
-      <c r="S13">
-        <v>1.38</v>
-      </c>
-      <c r="T13">
-        <v>2.7</v>
-      </c>
-      <c r="U13">
-        <v>2.91</v>
-      </c>
-      <c r="V13">
-        <v>1.33</v>
-      </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>1.27</v>
-      </c>
-      <c r="Z13">
-        <v>3.14</v>
-      </c>
-      <c r="AA13">
-        <v>1.98</v>
-      </c>
-      <c r="AB13">
-        <v>1.74</v>
-      </c>
-      <c r="AC13">
-        <v>3.42</v>
-      </c>
-      <c r="AD13">
-        <v>1.23</v>
-      </c>
-      <c r="AE13">
-        <v>1.06</v>
-      </c>
-      <c r="AF13">
-        <v>1.77</v>
-      </c>
-      <c r="AG13">
-        <v>1.92</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q14">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
+        <v>1.43</v>
+      </c>
+      <c r="T14">
+        <v>2.75</v>
+      </c>
+      <c r="U14">
+        <v>2.86</v>
+      </c>
+      <c r="V14">
         <v>1.31</v>
       </c>
-      <c r="T14">
-        <v>3.3</v>
-      </c>
-      <c r="U14">
-        <v>2.59</v>
-      </c>
-      <c r="V14">
-        <v>1.5</v>
-      </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
+        <v>1.33</v>
+      </c>
+      <c r="Z14">
+        <v>2.88</v>
+      </c>
+      <c r="AA14">
+        <v>2.09</v>
+      </c>
+      <c r="AB14">
+        <v>1.65</v>
+      </c>
+      <c r="AC14">
+        <v>3.9</v>
+      </c>
+      <c r="AD14">
         <v>1.22</v>
       </c>
-      <c r="Z14">
-        <v>3.9</v>
-      </c>
-      <c r="AA14">
-        <v>1.68</v>
-      </c>
-      <c r="AB14">
-        <v>2.02</v>
-      </c>
-      <c r="AC14">
-        <v>2.75</v>
-      </c>
-      <c r="AD14">
-        <v>1.4</v>
-      </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S15">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U15">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>2.88</v>
+        <v>3.43</v>
       </c>
       <c r="AA15">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AC15">
-        <v>3.9</v>
+        <v>3.43</v>
       </c>
       <c r="AD15">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T16">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="U16">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
+        <v>1.33</v>
+      </c>
+      <c r="Z16">
+        <v>2.88</v>
+      </c>
+      <c r="AA16">
+        <v>2.04</v>
+      </c>
+      <c r="AB16">
+        <v>1.69</v>
+      </c>
+      <c r="AC16">
+        <v>3.67</v>
+      </c>
+      <c r="AD16">
         <v>1.26</v>
       </c>
-      <c r="Z16">
-        <v>3.43</v>
-      </c>
-      <c r="AA16">
-        <v>1.93</v>
-      </c>
-      <c r="AB16">
-        <v>1.79</v>
-      </c>
-      <c r="AC16">
-        <v>3.43</v>
-      </c>
-      <c r="AD16">
-        <v>1.29</v>
-      </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3427,13 +3427,13 @@
         <v>2.32</v>
       </c>
       <c r="U19">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
         <v>1.1</v>
@@ -3448,7 +3448,7 @@
         <v>2.63</v>
       </c>
       <c r="AB19">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC19">
         <v>5.5</v>
@@ -3747,7 +3747,7 @@
         <v>2.05</v>
       </c>
       <c r="S21">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
         <v>2.62</v>
@@ -3762,13 +3762,13 @@
         <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z21">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA21">
         <v>2.25</v>
@@ -3780,10 +3780,10 @@
         <v>4.33</v>
       </c>
       <c r="AD21">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
         <v>1.89</v>
@@ -3901,7 +3901,7 @@
         <v>3.63</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q22">
         <v>2.05</v>
@@ -3928,16 +3928,16 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="AA22">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AB22">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
         <v>3.25</v>
@@ -3952,7 +3952,7 @@
         <v>2.15</v>
       </c>
       <c r="AG22">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T15">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="U15">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
+        <v>1.33</v>
+      </c>
+      <c r="Z15">
+        <v>2.88</v>
+      </c>
+      <c r="AA15">
+        <v>2.04</v>
+      </c>
+      <c r="AB15">
+        <v>1.69</v>
+      </c>
+      <c r="AC15">
+        <v>3.67</v>
+      </c>
+      <c r="AD15">
         <v>1.26</v>
       </c>
-      <c r="Z15">
-        <v>3.43</v>
-      </c>
-      <c r="AA15">
-        <v>1.93</v>
-      </c>
-      <c r="AB15">
-        <v>1.79</v>
-      </c>
-      <c r="AC15">
-        <v>3.43</v>
-      </c>
-      <c r="AD15">
-        <v>1.29</v>
-      </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG15">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,65 +2917,65 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R16">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>1.39</v>
+      </c>
+      <c r="T16">
+        <v>2.71</v>
+      </c>
+      <c r="U16">
+        <v>2.75</v>
+      </c>
+      <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.06</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.23</v>
+      </c>
+      <c r="Z16">
+        <v>3.42</v>
+      </c>
+      <c r="AA16">
+        <v>1.83</v>
+      </c>
+      <c r="AB16">
+        <v>1.84</v>
+      </c>
+      <c r="AC16">
+        <v>3.05</v>
+      </c>
+      <c r="AD16">
+        <v>1.28</v>
+      </c>
+      <c r="AE16">
+        <v>1.07</v>
+      </c>
+      <c r="AF16">
+        <v>1.62</v>
+      </c>
+      <c r="AG16">
         <v>2.05</v>
       </c>
-      <c r="S16">
-        <v>1.41</v>
-      </c>
-      <c r="T16">
-        <v>2.59</v>
-      </c>
-      <c r="U16">
-        <v>3</v>
-      </c>
-      <c r="V16">
-        <v>1.33</v>
-      </c>
-      <c r="W16">
-        <v>1.07</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.33</v>
-      </c>
-      <c r="Z16">
-        <v>2.88</v>
-      </c>
-      <c r="AA16">
-        <v>2.04</v>
-      </c>
-      <c r="AB16">
-        <v>1.69</v>
-      </c>
-      <c r="AC16">
-        <v>3.67</v>
-      </c>
-      <c r="AD16">
-        <v>1.26</v>
-      </c>
-      <c r="AE16">
-        <v>1.05</v>
-      </c>
-      <c r="AF16">
-        <v>1.81</v>
-      </c>
-      <c r="AG16">
-        <v>1.85</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
         <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.8</v>
+        <v>3.62</v>
       </c>
       <c r="Q18">
+        <v>2.4</v>
+      </c>
+      <c r="R18">
+        <v>2.06</v>
+      </c>
+      <c r="S18">
+        <v>1.38</v>
+      </c>
+      <c r="T18">
         <v>2.95</v>
       </c>
-      <c r="R18">
-        <v>2</v>
-      </c>
-      <c r="S18">
-        <v>1.39</v>
-      </c>
-      <c r="T18">
-        <v>2.71</v>
-      </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.26</v>
+      </c>
+      <c r="Z18">
+        <v>3.43</v>
+      </c>
+      <c r="AA18">
+        <v>1.93</v>
+      </c>
+      <c r="AB18">
+        <v>1.79</v>
+      </c>
+      <c r="AC18">
+        <v>3.43</v>
+      </c>
+      <c r="AD18">
+        <v>1.29</v>
+      </c>
+      <c r="AE18">
         <v>1.06</v>
       </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
-        <v>1.23</v>
-      </c>
-      <c r="Z18">
-        <v>3.42</v>
-      </c>
-      <c r="AA18">
+      <c r="AF18">
+        <v>1.77</v>
+      </c>
+      <c r="AG18">
+        <v>1.92</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.17</v>
+      </c>
+      <c r="AK18">
         <v>1.83</v>
-      </c>
-      <c r="AB18">
-        <v>1.84</v>
-      </c>
-      <c r="AC18">
-        <v>3.05</v>
-      </c>
-      <c r="AD18">
-        <v>1.28</v>
-      </c>
-      <c r="AE18">
-        <v>1.07</v>
-      </c>
-      <c r="AF18">
-        <v>1.62</v>
-      </c>
-      <c r="AG18">
-        <v>2.05</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.28</v>
-      </c>
-      <c r="AK18">
-        <v>1.5</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -638,22 +638,22 @@
         <v>2.7</v>
       </c>
       <c r="O2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P2">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="Q2">
         <v>3.44</v>
       </c>
       <c r="R2">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
         <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U2">
         <v>3.02</v>
@@ -662,7 +662,7 @@
         <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -671,16 +671,16 @@
         <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="AA2">
         <v>2</v>
       </c>
       <c r="AB2">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD2">
         <v>1.21</v>
@@ -692,7 +692,7 @@
         <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
         <v>1.4</v>
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
         <v>2.38</v>
       </c>
       <c r="S3">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U3">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V3">
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB3">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AD3">
         <v>1.44</v>
@@ -852,10 +852,10 @@
         <v>1.19</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -976,7 +976,7 @@
         <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
         <v>3</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
         <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
         <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
         <v>1.25</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q5">
-        <v>4.67</v>
+        <v>4.61</v>
       </c>
       <c r="R5">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S5">
         <v>1.39</v>
@@ -1145,7 +1145,7 @@
         <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V5">
         <v>1.38</v>
@@ -1157,31 +1157,31 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
         <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AC5">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="AD5">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
         <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
         <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="R6">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S6">
         <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="U6">
         <v>3.42</v>
@@ -1320,31 +1320,31 @@
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z6">
         <v>2.49</v>
       </c>
       <c r="AA6">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AB6">
         <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>4.72</v>
+        <v>4.76</v>
       </c>
       <c r="AD6">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE6">
         <v>1</v>
       </c>
       <c r="AF6">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="O8">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="P8">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="Q8">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R8">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="S8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U8">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V8">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="W8">
         <v>1.2</v>
@@ -1649,28 +1649,28 @@
         <v>1.05</v>
       </c>
       <c r="Z8">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB8">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AC8">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD8">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AE8">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AF8">
         <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK8">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Q9">
         <v>7</v>
       </c>
       <c r="R9">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S9">
         <v>1.22</v>
@@ -1800,40 +1800,40 @@
         <v>2.1</v>
       </c>
       <c r="V9">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA9">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB9">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="AC9">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD9">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE9">
         <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="R10">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.35</v>
@@ -1963,34 +1963,34 @@
         <v>2.66</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.62</v>
+        <v>3.28</v>
       </c>
       <c r="AA10">
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AD10">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
         <v>1.6</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK10">
         <v>1.5</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
         <v>3.25</v>
       </c>
       <c r="P11">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q11">
         <v>3.73</v>
       </c>
       <c r="R11">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S11">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V11">
         <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AA11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC11">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AD11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P12">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="Q12">
         <v>2.7</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S12">
         <v>1.38</v>
@@ -2286,43 +2286,43 @@
         <v>2.7</v>
       </c>
       <c r="U12">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
         <v>1.74</v>
       </c>
       <c r="AC12">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD12">
         <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
         <v>1.67</v>
@@ -2437,19 +2437,19 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R13">
         <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U13">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="V13">
         <v>1.5</v>
@@ -2461,22 +2461,22 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z13">
         <v>3.9</v>
       </c>
       <c r="AA13">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB13">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AC13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD13">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
@@ -2485,7 +2485,7 @@
         <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,34 +2591,34 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="V14">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.04</v>
@@ -2627,13 +2627,13 @@
         <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA14">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
         <v>3.9</v>
@@ -2648,7 +2648,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
         <v>2</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,65 +2754,65 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q15">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R15">
+        <v>2.06</v>
+      </c>
+      <c r="S15">
+        <v>1.38</v>
+      </c>
+      <c r="T15">
+        <v>2.73</v>
+      </c>
+      <c r="U15">
+        <v>2.62</v>
+      </c>
+      <c r="V15">
+        <v>1.4</v>
+      </c>
+      <c r="W15">
+        <v>1.06</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.23</v>
+      </c>
+      <c r="Z15">
+        <v>3.42</v>
+      </c>
+      <c r="AA15">
+        <v>1.83</v>
+      </c>
+      <c r="AB15">
+        <v>1.9</v>
+      </c>
+      <c r="AC15">
+        <v>3.05</v>
+      </c>
+      <c r="AD15">
+        <v>1.28</v>
+      </c>
+      <c r="AE15">
+        <v>1.08</v>
+      </c>
+      <c r="AF15">
+        <v>1.62</v>
+      </c>
+      <c r="AG15">
         <v>2.05</v>
       </c>
-      <c r="S15">
-        <v>1.41</v>
-      </c>
-      <c r="T15">
-        <v>2.59</v>
-      </c>
-      <c r="U15">
-        <v>3</v>
-      </c>
-      <c r="V15">
-        <v>1.33</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>1.33</v>
-      </c>
-      <c r="Z15">
-        <v>2.88</v>
-      </c>
-      <c r="AA15">
-        <v>2.04</v>
-      </c>
-      <c r="AB15">
-        <v>1.69</v>
-      </c>
-      <c r="AC15">
-        <v>3.67</v>
-      </c>
-      <c r="AD15">
-        <v>1.26</v>
-      </c>
-      <c r="AE15">
-        <v>1.05</v>
-      </c>
-      <c r="AF15">
-        <v>1.81</v>
-      </c>
-      <c r="AG15">
-        <v>1.85</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK15">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S16">
+        <v>1.34</v>
+      </c>
+      <c r="T16">
+        <v>3</v>
+      </c>
+      <c r="U16">
+        <v>2.66</v>
+      </c>
+      <c r="V16">
         <v>1.39</v>
-      </c>
-      <c r="T16">
-        <v>2.71</v>
-      </c>
-      <c r="U16">
-        <v>2.75</v>
-      </c>
-      <c r="V16">
-        <v>1.4</v>
       </c>
       <c r="W16">
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA16">
         <v>1.83</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AC16">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q17">
-        <v>3.6</v>
+        <v>2.54</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U17">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3113,31 +3113,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z17">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AB17">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC17">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="AD17">
         <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="R18">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="U18">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
+        <v>1.33</v>
+      </c>
+      <c r="Z18">
+        <v>2.7</v>
+      </c>
+      <c r="AA18">
+        <v>2.16</v>
+      </c>
+      <c r="AB18">
+        <v>1.56</v>
+      </c>
+      <c r="AC18">
+        <v>3.72</v>
+      </c>
+      <c r="AD18">
         <v>1.26</v>
       </c>
-      <c r="Z18">
-        <v>3.43</v>
-      </c>
-      <c r="AA18">
-        <v>1.93</v>
-      </c>
-      <c r="AB18">
-        <v>1.79</v>
-      </c>
-      <c r="AC18">
-        <v>3.43</v>
-      </c>
-      <c r="AD18">
-        <v>1.29</v>
-      </c>
       <c r="AE18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK18">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,37 +3412,37 @@
         <v>3</v>
       </c>
       <c r="P19">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="R19">
         <v>1.91</v>
       </c>
       <c r="S19">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="T19">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U19">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V19">
         <v>1.23</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Z19">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AA19">
         <v>2.63</v>
@@ -3454,7 +3454,7 @@
         <v>5.5</v>
       </c>
       <c r="AD19">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
@@ -3463,7 +3463,7 @@
         <v>2.05</v>
       </c>
       <c r="AG19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
         <v>2.75</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R20">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="U20">
         <v>2.85</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,13 +3602,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AA20">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AB20">
         <v>1.81</v>
@@ -3620,7 +3620,7 @@
         <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
         <v>1.7</v>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3750,7 +3750,7 @@
         <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U21">
         <v>3.16</v>
@@ -3771,13 +3771,13 @@
         <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB21">
         <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD21">
         <v>1.22</v>
@@ -3786,10 +3786,10 @@
         <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG21">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="O22">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
         <v>2.05</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S22">
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
         <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
         <v>1.07</v>
@@ -3931,25 +3931,25 @@
         <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="AA22">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
         <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG22">
         <v>1.67</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O2">
         <v>3.15</v>
       </c>
       <c r="P2">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="Q2">
         <v>3.44</v>
@@ -656,10 +656,10 @@
         <v>2.63</v>
       </c>
       <c r="U2">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
         <v>1.06</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
         <v>1.36</v>
@@ -994,7 +994,7 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
         <v>3.5</v>
@@ -1018,7 +1018,7 @@
         <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1459,22 +1459,22 @@
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
         <v>1.18</v>
@@ -1483,31 +1483,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA7">
         <v>1.39</v>
       </c>
       <c r="AB7">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AC7">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AD7">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AE7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
         <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
+        <v>3.05</v>
+      </c>
+      <c r="P11">
         <v>3.25</v>
       </c>
-      <c r="P11">
-        <v>2.15</v>
-      </c>
       <c r="Q11">
-        <v>3.73</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
+        <v>2.05</v>
+      </c>
+      <c r="S11">
+        <v>1.38</v>
+      </c>
+      <c r="T11">
+        <v>2.7</v>
+      </c>
+      <c r="U11">
+        <v>2.75</v>
+      </c>
+      <c r="V11">
+        <v>1.38</v>
+      </c>
+      <c r="W11">
+        <v>1.07</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.29</v>
+      </c>
+      <c r="Z11">
+        <v>3.3</v>
+      </c>
+      <c r="AA11">
         <v>1.95</v>
       </c>
-      <c r="S11">
-        <v>1.4</v>
-      </c>
-      <c r="T11">
-        <v>2.5</v>
-      </c>
-      <c r="U11">
-        <v>2.9</v>
-      </c>
-      <c r="V11">
+      <c r="AB11">
+        <v>1.74</v>
+      </c>
+      <c r="AC11">
+        <v>3.6</v>
+      </c>
+      <c r="AD11">
+        <v>1.23</v>
+      </c>
+      <c r="AE11">
+        <v>1.04</v>
+      </c>
+      <c r="AF11">
+        <v>1.73</v>
+      </c>
+      <c r="AG11">
+        <v>1.93</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.33</v>
       </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>1.36</v>
-      </c>
-      <c r="Z11">
-        <v>2.95</v>
-      </c>
-      <c r="AA11">
-        <v>2.1</v>
-      </c>
-      <c r="AB11">
-        <v>1.64</v>
-      </c>
-      <c r="AC11">
-        <v>3.75</v>
-      </c>
-      <c r="AD11">
-        <v>1.25</v>
-      </c>
-      <c r="AE11">
-        <v>1.03</v>
-      </c>
-      <c r="AF11">
-        <v>1.8</v>
-      </c>
-      <c r="AG11">
-        <v>1.83</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.3</v>
-      </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="R12">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="AC12">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG12">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q13">
+        <v>2.32</v>
+      </c>
+      <c r="R13">
         <v>2.21</v>
       </c>
-      <c r="R13">
-        <v>2.25</v>
-      </c>
       <c r="S13">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
         <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
+        <v>3.1</v>
+      </c>
+      <c r="AA13">
+        <v>2.12</v>
+      </c>
+      <c r="AB13">
+        <v>1.67</v>
+      </c>
+      <c r="AC13">
         <v>3.9</v>
       </c>
-      <c r="AA13">
-        <v>1.7</v>
-      </c>
-      <c r="AB13">
-        <v>2.12</v>
-      </c>
-      <c r="AC13">
-        <v>2.7</v>
-      </c>
       <c r="AD13">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG13">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.32</v>
+        <v>3.08</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="U14">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA14">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC14">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,65 +2917,65 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.08</v>
+        <v>3.73</v>
       </c>
       <c r="R16">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="W16">
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AA16">
+        <v>2.1</v>
+      </c>
+      <c r="AB16">
+        <v>1.64</v>
+      </c>
+      <c r="AC16">
+        <v>3.75</v>
+      </c>
+      <c r="AD16">
+        <v>1.25</v>
+      </c>
+      <c r="AE16">
+        <v>1.03</v>
+      </c>
+      <c r="AF16">
+        <v>1.8</v>
+      </c>
+      <c r="AG16">
         <v>1.83</v>
       </c>
-      <c r="AB16">
-        <v>1.93</v>
-      </c>
-      <c r="AC16">
-        <v>3.15</v>
-      </c>
-      <c r="AD16">
-        <v>1.26</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.65</v>
-      </c>
-      <c r="AG16">
-        <v>1.97</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
+        <v>1.3</v>
+      </c>
+      <c r="AK16">
         <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.32</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3753,13 +3753,13 @@
         <v>2.63</v>
       </c>
       <c r="U21">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
         <v>1.08</v>
@@ -3771,25 +3771,25 @@
         <v>3.1</v>
       </c>
       <c r="AA21">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
         <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF21">
         <v>1.9</v>
       </c>
       <c r="AG21">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>3.5</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q22">
         <v>2.05</v>
@@ -3931,10 +3931,10 @@
         <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>3.11</v>
+        <v>2.88</v>
       </c>
       <c r="AA22">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
         <v>1.73</v>
@@ -3946,13 +3946,13 @@
         <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
         <v>2.05</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q14">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="R14">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="S14">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U14">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="V14">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
         <v>1.06</v>
@@ -2627,44 +2627,44 @@
         <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AA14">
+        <v>1.91</v>
+      </c>
+      <c r="AB14">
+        <v>1.79</v>
+      </c>
+      <c r="AC14">
+        <v>3.45</v>
+      </c>
+      <c r="AD14">
+        <v>1.3</v>
+      </c>
+      <c r="AE14">
+        <v>1.06</v>
+      </c>
+      <c r="AF14">
+        <v>1.77</v>
+      </c>
+      <c r="AG14">
+        <v>1.92</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.17</v>
+      </c>
+      <c r="AK14">
         <v>1.83</v>
-      </c>
-      <c r="AB14">
-        <v>1.93</v>
-      </c>
-      <c r="AC14">
-        <v>3.15</v>
-      </c>
-      <c r="AD14">
-        <v>1.26</v>
-      </c>
-      <c r="AE14">
-        <v>1.08</v>
-      </c>
-      <c r="AF14">
-        <v>1.65</v>
-      </c>
-      <c r="AG14">
-        <v>1.97</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.25</v>
-      </c>
-      <c r="AK14">
-        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
         <v>1.06</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA15">
         <v>1.83</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC15">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
         <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q16">
-        <v>3.73</v>
+        <v>2.9</v>
       </c>
       <c r="R16">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
+        <v>1.38</v>
+      </c>
+      <c r="T16">
+        <v>2.73</v>
+      </c>
+      <c r="U16">
+        <v>2.62</v>
+      </c>
+      <c r="V16">
         <v>1.4</v>
-      </c>
-      <c r="T16">
-        <v>2.5</v>
-      </c>
-      <c r="U16">
-        <v>2.9</v>
-      </c>
-      <c r="V16">
-        <v>1.33</v>
       </c>
       <c r="W16">
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB16">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE16">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>3.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>2.54</v>
+        <v>3.73</v>
       </c>
       <c r="R17">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AA17">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AB17">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="AC17">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AD17">
+        <v>1.25</v>
+      </c>
+      <c r="AE17">
+        <v>1.03</v>
+      </c>
+      <c r="AF17">
+        <v>1.8</v>
+      </c>
+      <c r="AG17">
+        <v>1.83</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.3</v>
       </c>
-      <c r="AE17">
-        <v>1.06</v>
-      </c>
-      <c r="AF17">
-        <v>1.77</v>
-      </c>
-      <c r="AG17">
-        <v>1.92</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.17</v>
-      </c>
       <c r="AK17">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -644,16 +644,16 @@
         <v>2.36</v>
       </c>
       <c r="Q2">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R2">
         <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
         <v>3.01</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
         <v>3.2</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -997,28 +997,28 @@
         <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
         <v>1.3</v>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>4.61</v>
+        <v>3.59</v>
       </c>
       <c r="R5">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="S5">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>2.39</v>
       </c>
       <c r="U5">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
         <v>1.04</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AB5">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AC5">
-        <v>3.49</v>
+        <v>4.64</v>
       </c>
       <c r="AD5">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-20 12:00:00</t>
+          <t>2026-08-20 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="Q6">
-        <v>3.61</v>
+        <v>4.69</v>
       </c>
       <c r="R6">
+        <v>2.04</v>
+      </c>
+      <c r="S6">
+        <v>1.44</v>
+      </c>
+      <c r="T6">
+        <v>2.54</v>
+      </c>
+      <c r="U6">
+        <v>3.07</v>
+      </c>
+      <c r="V6">
+        <v>1.32</v>
+      </c>
+      <c r="W6">
+        <v>1.02</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.32</v>
+      </c>
+      <c r="Z6">
+        <v>2.88</v>
+      </c>
+      <c r="AA6">
+        <v>2.12</v>
+      </c>
+      <c r="AB6">
+        <v>1.78</v>
+      </c>
+      <c r="AC6">
+        <v>3.66</v>
+      </c>
+      <c r="AD6">
+        <v>1.21</v>
+      </c>
+      <c r="AE6">
+        <v>1.04</v>
+      </c>
+      <c r="AF6">
+        <v>1.84</v>
+      </c>
+      <c r="AG6">
+        <v>1.86</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.91</v>
       </c>
-      <c r="S6">
-        <v>1.5</v>
-      </c>
-      <c r="T6">
-        <v>2.39</v>
-      </c>
-      <c r="U6">
-        <v>3.42</v>
-      </c>
-      <c r="V6">
-        <v>1.26</v>
-      </c>
-      <c r="W6">
-        <v>1</v>
-      </c>
-      <c r="X6">
-        <v>1.04</v>
-      </c>
-      <c r="Y6">
-        <v>1.47</v>
-      </c>
-      <c r="Z6">
-        <v>2.49</v>
-      </c>
-      <c r="AA6">
-        <v>2.47</v>
-      </c>
-      <c r="AB6">
-        <v>1.56</v>
-      </c>
-      <c r="AC6">
-        <v>4.76</v>
-      </c>
-      <c r="AD6">
-        <v>1.18</v>
-      </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6">
-        <v>2.01</v>
-      </c>
-      <c r="AG6">
-        <v>1.72</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.29</v>
-      </c>
       <c r="AK6">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-20 12:30:00</t>
+          <t>2026-08-20 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T16">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="U16">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AA16">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="AC16">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q17">
-        <v>3.73</v>
+        <v>2.9</v>
       </c>
       <c r="R17">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.73</v>
+      </c>
+      <c r="U17">
+        <v>2.62</v>
+      </c>
+      <c r="V17">
         <v>1.4</v>
-      </c>
-      <c r="T17">
-        <v>2.5</v>
-      </c>
-      <c r="U17">
-        <v>2.9</v>
-      </c>
-      <c r="V17">
-        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB17">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK17">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q18">
-        <v>2.94</v>
+        <v>3.73</v>
       </c>
       <c r="R18">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA18">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB18">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AC18">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -701,7 +701,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,51 +775,51 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P3">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q3">
         <v>2.63</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.25</v>
       </c>
       <c r="T3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V3">
         <v>1.5</v>
@@ -834,7 +834,7 @@
         <v>1.18</v>
       </c>
       <c r="Z3">
-        <v>4.15</v>
+        <v>4.57</v>
       </c>
       <c r="AA3">
         <v>1.62</v>
@@ -843,7 +843,7 @@
         <v>2.25</v>
       </c>
       <c r="AC3">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AD3">
         <v>1.44</v>
@@ -859,46 +859,46 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "67"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "79"]</t>
         </is>
       </c>
       <c r="AJ3">
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "47", "77"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1116,115 +1116,115 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q5">
-        <v>3.59</v>
+        <v>3.35</v>
       </c>
       <c r="R5">
         <v>1.89</v>
       </c>
       <c r="S5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T5">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U5">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
         <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z5">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="AA5">
         <v>2.42</v>
       </c>
       <c r="AB5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AC5">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="AD5">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AG5">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "45+3"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ5">
         <v>1.36</v>
       </c>
       <c r="AK5">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "44"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,130 +1427,130 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T7">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U7">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA7">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AB7">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD7">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG7">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "8", "90+1"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78", "85"]</t>
         </is>
       </c>
       <c r="AJ7">
         <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1609,111 +1609,111 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="O8">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="P8">
-        <v>7.3</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="Q8">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="S8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U8">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="V8">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z8">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB8">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AC8">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD8">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AE8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF8">
         <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>["43"]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ8">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1779,74 +1779,74 @@
         <v>10</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>6.65</v>
       </c>
       <c r="P9">
         <v>1.21</v>
       </c>
       <c r="Q9">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R9">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U9">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="W9">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
+        <v>1.19</v>
+      </c>
+      <c r="Z9">
+        <v>4.55</v>
+      </c>
+      <c r="AA9">
+        <v>1.55</v>
+      </c>
+      <c r="AB9">
+        <v>2.3</v>
+      </c>
+      <c r="AC9">
+        <v>2.45</v>
+      </c>
+      <c r="AD9">
+        <v>1.52</v>
+      </c>
+      <c r="AE9">
+        <v>1.18</v>
+      </c>
+      <c r="AF9">
+        <v>2.15</v>
+      </c>
+      <c r="AG9">
+        <v>1.63</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.11</v>
-      </c>
-      <c r="Z9">
-        <v>5.5</v>
-      </c>
-      <c r="AA9">
-        <v>1.45</v>
-      </c>
-      <c r="AB9">
-        <v>2.72</v>
-      </c>
-      <c r="AC9">
-        <v>2.05</v>
-      </c>
-      <c r="AD9">
-        <v>1.69</v>
-      </c>
-      <c r="AE9">
-        <v>1.25</v>
-      </c>
-      <c r="AF9">
-        <v>1.8</v>
-      </c>
-      <c r="AG9">
-        <v>1.83</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.1</v>
       </c>
       <c r="AK9">
         <v>1.04</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q10">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
+        <v>1.28</v>
+      </c>
+      <c r="Z10">
+        <v>3.3</v>
+      </c>
+      <c r="AA10">
+        <v>1.95</v>
+      </c>
+      <c r="AB10">
+        <v>1.75</v>
+      </c>
+      <c r="AC10">
+        <v>3.6</v>
+      </c>
+      <c r="AD10">
         <v>1.25</v>
       </c>
-      <c r="Z10">
-        <v>3.28</v>
-      </c>
-      <c r="AA10">
-        <v>1.85</v>
-      </c>
-      <c r="AB10">
-        <v>1.85</v>
-      </c>
-      <c r="AC10">
-        <v>3.04</v>
-      </c>
-      <c r="AD10">
-        <v>1.29</v>
-      </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O11">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q11">
+        <v>2.17</v>
+      </c>
+      <c r="R11">
+        <v>2.41</v>
+      </c>
+      <c r="S11">
+        <v>1.29</v>
+      </c>
+      <c r="T11">
+        <v>2.95</v>
+      </c>
+      <c r="U11">
+        <v>2.38</v>
+      </c>
+      <c r="V11">
+        <v>1.5</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.21</v>
+      </c>
+      <c r="Z11">
+        <v>3.95</v>
+      </c>
+      <c r="AA11">
+        <v>1.67</v>
+      </c>
+      <c r="AB11">
+        <v>2.18</v>
+      </c>
+      <c r="AC11">
         <v>2.7</v>
       </c>
-      <c r="R11">
+      <c r="AD11">
+        <v>1.42</v>
+      </c>
+      <c r="AE11">
+        <v>1.13</v>
+      </c>
+      <c r="AF11">
+        <v>1.61</v>
+      </c>
+      <c r="AG11">
+        <v>2.16</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.25</v>
+      </c>
+      <c r="AK11">
         <v>2.05</v>
-      </c>
-      <c r="S11">
-        <v>1.38</v>
-      </c>
-      <c r="T11">
-        <v>2.7</v>
-      </c>
-      <c r="U11">
-        <v>2.75</v>
-      </c>
-      <c r="V11">
-        <v>1.38</v>
-      </c>
-      <c r="W11">
-        <v>1.07</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.29</v>
-      </c>
-      <c r="Z11">
-        <v>3.3</v>
-      </c>
-      <c r="AA11">
-        <v>1.95</v>
-      </c>
-      <c r="AB11">
-        <v>1.74</v>
-      </c>
-      <c r="AC11">
-        <v>3.6</v>
-      </c>
-      <c r="AD11">
-        <v>1.23</v>
-      </c>
-      <c r="AE11">
-        <v>1.04</v>
-      </c>
-      <c r="AF11">
-        <v>1.73</v>
-      </c>
-      <c r="AG11">
-        <v>1.93</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.33</v>
-      </c>
-      <c r="AK11">
-        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q12">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="U12">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA12">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AB12">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="AC12">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AD12">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF12">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG12">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P13">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>2.32</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U13">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="V13">
         <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AA13">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AB13">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AC13">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK13">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G14">
@@ -2594,61 +2594,61 @@
         <v>2</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="Q14">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="R14">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="U14">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14">
         <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
         <v>1.34</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.06</v>
@@ -2793,10 +2793,10 @@
         <v>3.25</v>
       </c>
       <c r="AA15">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB15">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
         <v>3.15</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK15">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q16">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
+        <v>1.33</v>
+      </c>
+      <c r="T16">
+        <v>2.88</v>
+      </c>
+      <c r="U16">
+        <v>2.62</v>
+      </c>
+      <c r="V16">
         <v>1.41</v>
       </c>
-      <c r="T16">
-        <v>2.45</v>
-      </c>
-      <c r="U16">
-        <v>3</v>
-      </c>
-      <c r="V16">
-        <v>1.35</v>
-      </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA16">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>1.56</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="Q17">
-        <v>2.9</v>
+        <v>3.87</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="AA17">
+        <v>2.1</v>
+      </c>
+      <c r="AB17">
+        <v>1.67</v>
+      </c>
+      <c r="AC17">
+        <v>4.1</v>
+      </c>
+      <c r="AD17">
+        <v>1.19</v>
+      </c>
+      <c r="AE17">
+        <v>1.03</v>
+      </c>
+      <c r="AF17">
+        <v>1.8</v>
+      </c>
+      <c r="AG17">
         <v>1.83</v>
       </c>
-      <c r="AB17">
-        <v>1.9</v>
-      </c>
-      <c r="AC17">
-        <v>3.05</v>
-      </c>
-      <c r="AD17">
-        <v>1.28</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
-      <c r="AF17">
-        <v>1.62</v>
-      </c>
-      <c r="AG17">
-        <v>2.05</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="O18">
         <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.15</v>
+        <v>4.25</v>
       </c>
       <c r="Q18">
-        <v>3.73</v>
+        <v>2.45</v>
       </c>
       <c r="R18">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="S18">
         <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="U18">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
         <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA18">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB18">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AC18">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AD18">
         <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,77 +3409,77 @@
         <v>2.25</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P19">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="Q19">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="R19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S19">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U19">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="V19">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W19">
         <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="AA19">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AB19">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AC19">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD19">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
+        <v>1.73</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.26</v>
+      </c>
+      <c r="AK19">
         <v>1.62</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.25</v>
-      </c>
-      <c r="AK19">
-        <v>1.64</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,22 +3569,22 @@
         </is>
       </c>
       <c r="N20">
+        <v>2.7</v>
+      </c>
+      <c r="O20">
+        <v>3.4</v>
+      </c>
+      <c r="P20">
         <v>2.45</v>
       </c>
-      <c r="O20">
-        <v>3.2</v>
-      </c>
-      <c r="P20">
-        <v>2.75</v>
-      </c>
       <c r="Q20">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="R20">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T20">
         <v>2.85</v>
@@ -3599,16 +3599,16 @@
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AA20">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AB20">
         <v>1.81</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK20">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -3750,13 +3750,13 @@
         <v>1.44</v>
       </c>
       <c r="T21">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="U21">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
         <v>1.01</v>
@@ -3765,19 +3765,19 @@
         <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z21">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB21">
         <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD21">
         <v>1.2</v>
@@ -3786,10 +3786,10 @@
         <v>1.02</v>
       </c>
       <c r="AF21">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG21">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3907,13 +3907,13 @@
         <v>2.05</v>
       </c>
       <c r="R22">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="S22">
         <v>1.36</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U22">
         <v>2.9</v>
@@ -3925,10 +3925,10 @@
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
         <v>2.88</v>
@@ -3937,22 +3937,22 @@
         <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC22">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE22">
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-08-20.xlsx
+++ b/jogos_2026-08-20.xlsx
@@ -1756,23 +1756,23 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "46", "88"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "77"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "45+1", "67"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2070,22 +2070,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,84 +2098,84 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="P11">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q11">
-        <v>2.17</v>
+        <v>2.9</v>
       </c>
       <c r="R11">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
+        <v>1.36</v>
+      </c>
+      <c r="Z11">
+        <v>2.7</v>
+      </c>
+      <c r="AA11">
+        <v>2.16</v>
+      </c>
+      <c r="AB11">
+        <v>1.56</v>
+      </c>
+      <c r="AC11">
+        <v>3.58</v>
+      </c>
+      <c r="AD11">
         <v>1.21</v>
       </c>
-      <c r="Z11">
-        <v>3.95</v>
-      </c>
-      <c r="AA11">
-        <v>1.67</v>
-      </c>
-      <c r="AB11">
-        <v>2.18</v>
-      </c>
-      <c r="AC11">
-        <v>2.7</v>
-      </c>
-      <c r="AD11">
-        <v>1.42</v>
-      </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF11">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>["42"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2199,10 +2199,10 @@
         <v>0</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2233,22 +2233,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2257,88 +2257,88 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12">
+        <v>3.2</v>
+      </c>
+      <c r="P12">
+        <v>3.25</v>
+      </c>
+      <c r="Q12">
+        <v>2.63</v>
+      </c>
+      <c r="R12">
+        <v>2.2</v>
+      </c>
+      <c r="S12">
+        <v>1.33</v>
+      </c>
+      <c r="T12">
+        <v>2.88</v>
+      </c>
+      <c r="U12">
+        <v>2.62</v>
+      </c>
+      <c r="V12">
+        <v>1.41</v>
+      </c>
+      <c r="W12">
+        <v>1.06</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1.22</v>
+      </c>
+      <c r="Z12">
+        <v>3.5</v>
+      </c>
+      <c r="AA12">
+        <v>1.79</v>
+      </c>
+      <c r="AB12">
+        <v>1.9</v>
+      </c>
+      <c r="AC12">
+        <v>2.88</v>
+      </c>
+      <c r="AD12">
+        <v>1.29</v>
+      </c>
+      <c r="AE12">
+        <v>1.08</v>
+      </c>
+      <c r="AF12">
         <v>1.67</v>
       </c>
-      <c r="O12">
-        <v>3.55</v>
-      </c>
-      <c r="P12">
-        <v>4.4</v>
-      </c>
-      <c r="Q12">
-        <v>2.32</v>
-      </c>
-      <c r="R12">
-        <v>2.23</v>
-      </c>
-      <c r="S12">
-        <v>1.4</v>
-      </c>
-      <c r="T12">
-        <v>2.6</v>
-      </c>
-      <c r="U12">
-        <v>2.9</v>
-      </c>
-      <c r="V12">
-        <v>1.35</v>
-      </c>
-      <c r="W12">
-        <v>1.07</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.33</v>
-      </c>
-      <c r="Z12">
-        <v>3.1</v>
-      </c>
-      <c r="AA12">
-        <v>2.12</v>
-      </c>
-      <c r="AB12">
-        <v>1.66</v>
-      </c>
-      <c r="AC12">
-        <v>3.4</v>
-      </c>
-      <c r="AD12">
-        <v>1.22</v>
-      </c>
-      <c r="AE12">
-        <v>1.05</v>
-      </c>
-      <c r="AF12">
-        <v>1.91</v>
-      </c>
       <c r="AG12">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2362,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,112 +2396,112 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.02</v>
+        <v>2.87</v>
       </c>
       <c r="O13">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q13">
-        <v>2.9</v>
+        <v>3.87</v>
       </c>
       <c r="R13">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
         <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA13">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB13">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD13">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF13">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG13">
         <v>1.83</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "54"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK13">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2525,10 +2525,10 @@
         <v>0</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,25 +2559,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -2587,29 +2587,29 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>2.89</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
         <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U14">
         <v>2.62</v>
@@ -2618,37 +2618,37 @@
         <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AD14">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG14">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "34"]</t>
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AK14">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2688,10 +2688,10 @@
         <v>0</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,139 +2722,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>2.89</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S15">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="U15">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA15">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AD15">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>["14", "34", "85"]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ15">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2885,16 +2885,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2906,79 +2906,79 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
-        <v>2.63</v>
+        <v>2.17</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U16">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA16">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AC16">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG16">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3014,10 +3014,10 @@
         <v>0</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,100 +3048,100 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.87</v>
+        <v>1.87</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>3.87</v>
+        <v>2.45</v>
       </c>
       <c r="R17">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="S17">
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Z17">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB17">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC17">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "56"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,113 +3211,113 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q18">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="R18">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
+        <v>1.38</v>
+      </c>
+      <c r="T18">
+        <v>2.82</v>
+      </c>
+      <c r="U18">
+        <v>2.62</v>
+      </c>
+      <c r="V18">
         <v>1.4</v>
       </c>
-      <c r="T18">
-        <v>2.95</v>
-      </c>
-      <c r="U18">
-        <v>2.65</v>
-      </c>
-      <c r="V18">
-        <v>1.35</v>
-      </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB18">
+        <v>1.78</v>
+      </c>
+      <c r="AC18">
+        <v>3.04</v>
+      </c>
+      <c r="AD18">
+        <v>1.34</v>
+      </c>
+      <c r="AE18">
+        <v>1.12</v>
+      </c>
+      <c r="AF18">
+        <v>1.67</v>
+      </c>
+      <c r="AG18">
+        <v>2.06</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>["32", "61"]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.22</v>
+      </c>
+      <c r="AK18">
         <v>1.73</v>
       </c>
-      <c r="AC18">
-        <v>3.3</v>
-      </c>
-      <c r="AD18">
-        <v>1.25</v>
-      </c>
-      <c r="AE18">
-        <v>1.07</v>
-      </c>
-      <c r="AF18">
-        <v>1.77</v>
-      </c>
-      <c r="AG18">
-        <v>1.92</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.3</v>
-      </c>
-      <c r="AK18">
-        <v>1.8</v>
-      </c>
       <c r="AL18">
         <v>0</v>
       </c>
@@ -3340,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3395,14 +3395,14 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3561,11 +3561,11 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O21">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="P21">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -3783,7 +3783,7 @@
         <v>1.2</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF21">
         <v>1.92</v>
@@ -3907,7 +3907,7 @@
         <v>2.05</v>
       </c>
       <c r="R22">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
         <v>1.36</v>
@@ -3931,10 +3931,10 @@
         <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
         <v>1.74</v>
@@ -3943,7 +3943,7 @@
         <v>3.45</v>
       </c>
       <c r="AD22">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE22">
         <v>1.08</v>
@@ -3952,7 +3952,7 @@
         <v>2.1</v>
       </c>
       <c r="AG22">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK22">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AL22">
         <v>0</v>
